--- a/contest_entry_forms/026_song_relay_competition_results--contest_entry_forms.xlsx
+++ b/contest_entry_forms/026_song_relay_competition_results--contest_entry_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ranking</t>
+          <t>ranking_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Ranking 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>judges_name</t>
+          <t>judges_name_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Judge Name</t>
+          <t>Judges Name 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>judge_score</t>
+          <t>judge_score_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Judge Score 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>song_name</t>
+          <t>song_name_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Song Name</t>
+          <t>Song Name 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>artist_name</t>
+          <t>artist_name_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Judge Name</t>
+          <t>Judge Name (3)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Song Relay Competition Results Score</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Submission Notes</t>
+          <t>Submission Notes (2)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>submission_date</t>
+          <t>submission_date_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Submission Date</t>
+          <t>Submission Date 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>judge_name</t>
+          <t>judge_name_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Judge Name</t>
+          <t>Judge Name 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,51 +1126,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ranking_choices</t>
+          <t>ranking_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ranking_choices</t>
+          <t>ranking_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ranking_choices</t>
+          <t>ranking_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
